--- a/Database Sistem.xlsx
+++ b/Database Sistem.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="User" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Users" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Pengadaan" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="Pekerjaan" sheetId="3" r:id="rId7"/>
     <sheet state="visible" name="RAB" sheetId="4" r:id="rId8"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="155">
   <si>
     <t>id</t>
   </si>
@@ -35,199 +35,226 @@
     <t>pekerjaan_id</t>
   </si>
   <si>
+    <t>nomor_paket</t>
+  </si>
+  <si>
+    <t>nomor_pengadaan</t>
+  </si>
+  <si>
+    <t>nama</t>
+  </si>
+  <si>
     <t>nama_pekerjaan</t>
   </si>
   <si>
-    <t>nomor_pengadaan</t>
+    <t>tahun</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>sumber_anggaran</t>
   </si>
   <si>
     <t>kategori</t>
   </si>
   <si>
-    <t>tahun</t>
+    <t>nilai_pagu</t>
   </si>
   <si>
     <t>uraian</t>
   </si>
   <si>
-    <t>sumber_anggaran</t>
+    <t>password</t>
+  </si>
+  <si>
+    <t>keterangan</t>
+  </si>
+  <si>
+    <t>created_at</t>
+  </si>
+  <si>
+    <t>ID_1789909514630390</t>
+  </si>
+  <si>
+    <t>jenis_tegangan</t>
+  </si>
+  <si>
+    <t>Pekerjaan Pengadaan Material Non MDU dan Jasa Konstruksi SKUTR Program Penggantian Komponen JTR</t>
   </si>
   <si>
     <t>satuan</t>
   </si>
   <si>
-    <t>nilai_pagu</t>
+    <t>email</t>
   </si>
   <si>
     <t>volume</t>
   </si>
   <si>
-    <t>nomor_paket</t>
+    <t>ABPN</t>
+  </si>
+  <si>
+    <t>role</t>
   </si>
   <si>
     <t>harga_material</t>
   </si>
   <si>
-    <t>keterangan</t>
+    <t>ID_1789910407476866</t>
   </si>
   <si>
     <t>harga_jasa</t>
   </si>
   <si>
-    <t>created_at</t>
+    <t>status</t>
+  </si>
+  <si>
+    <t>Pekerjaan Pengadaan Material Non MDU dan Jasa Konstruksi SUTM SKUTM SKTM Gardu Kubikel App TM App 3 Phasa TR Besar Catu Daya Dan SPKLU Program Pemasaran</t>
   </si>
   <si>
     <t>bagian_material</t>
   </si>
   <si>
+    <t>bagian_jasa</t>
+  </si>
+  <si>
+    <t>timestamp</t>
+  </si>
+  <si>
+    <t>APLN</t>
+  </si>
+  <si>
+    <t>jumlah</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>ID_1789918500044994</t>
+  </si>
+  <si>
+    <t>ID_1789925153933719</t>
+  </si>
+  <si>
+    <t>Pekerjaan Pengadaan Material Non MDU dan Jasa Konstruksi Gardu Program Manajemen Trafo</t>
+  </si>
+  <si>
+    <t>APBN</t>
+  </si>
+  <si>
+    <t>ID_1789924736760806</t>
+  </si>
+  <si>
     <t>jenis_kegiatan</t>
   </si>
   <si>
-    <t>bagian_jasa</t>
-  </si>
-  <si>
-    <t>ID_1789909514630390</t>
-  </si>
-  <si>
-    <t>nama</t>
-  </si>
-  <si>
-    <t>Pekerjaan Pengadaan Material Non MDU dan Jasa Konstruksi SKUTR Program Penggantian Komponen JTR</t>
-  </si>
-  <si>
-    <t>jumlah</t>
+    <t>ID_1789924393899358</t>
+  </si>
+  <si>
+    <t>supardiana</t>
+  </si>
+  <si>
+    <t>Pemasangan SUTM (AAACS 70-240 mm2) Per Kilometer</t>
+  </si>
+  <si>
+    <t>Umum</t>
   </si>
   <si>
     <t>volume_paket</t>
   </si>
   <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>ABPN</t>
+    <t>agus150385</t>
+  </si>
+  <si>
+    <t>TRECKSCHOOR TM</t>
+  </si>
+  <si>
+    <t>goespar@gmail.com</t>
   </si>
   <si>
     <t>lokasi</t>
   </si>
   <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>status</t>
+    <t>btg</t>
+  </si>
+  <si>
+    <t>Administrator</t>
+  </si>
+  <si>
+    <t>Aktif</t>
+  </si>
+  <si>
+    <t>tahun_anggaran</t>
   </si>
   <si>
     <t>progress</t>
   </si>
   <si>
-    <t>ID_1789910526865759</t>
-  </si>
-  <si>
-    <t>ID_1789910407476866</t>
-  </si>
-  <si>
     <t>updated_at</t>
   </si>
   <si>
-    <t>Pekerjaan Pengadaan Material Non MDU dan Jasa Konstruksi SUTM SKUTM SKTM Gardu Kubikel App TM App 3 Phasa TR Besar Catu Daya Dan SPKLU Program Pemasaran</t>
-  </si>
-  <si>
-    <t>ID_1789910470244103</t>
-  </si>
-  <si>
-    <t>ID_1789909573803619</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>Pemasangan SUTM (AAACS 70-240 mm2) Per Kilometer</t>
+    <t>ID_1789924325886631</t>
+  </si>
+  <si>
+    <t>ID_1789925228799211</t>
+  </si>
+  <si>
+    <t>Pembongkaran 1 Unit Gardu Portal 160-250 kVA 4 Jurusan</t>
+  </si>
+  <si>
+    <t>JTR</t>
+  </si>
+  <si>
+    <t>Pembongkaran</t>
+  </si>
+  <si>
+    <t>Arm Tie</t>
+  </si>
+  <si>
+    <t>5 unit</t>
+  </si>
+  <si>
+    <t>meter</t>
+  </si>
+  <si>
+    <t>Sawan</t>
   </si>
   <si>
     <t>JTM</t>
   </si>
   <si>
-    <t>role</t>
+    <t>ID_1789925346973368</t>
+  </si>
+  <si>
+    <t>pemasangan</t>
   </si>
   <si>
     <t>Kabel TIC 3 x 70 + 1 x 54.6 mm2</t>
   </si>
   <si>
-    <t>meter</t>
+    <t>Buleleng</t>
+  </si>
+  <si>
+    <t>ID_1789925436699626</t>
+  </si>
+  <si>
+    <t>ID_1789925513820403</t>
   </si>
   <si>
     <t>Pemasangan JTR Per Kilometer</t>
   </si>
   <si>
-    <t>Pasang JTR</t>
-  </si>
-  <si>
-    <t>timestamp</t>
-  </si>
-  <si>
-    <t>10 kms</t>
-  </si>
-  <si>
-    <t>Buleleng</t>
-  </si>
-  <si>
-    <t>user</t>
-  </si>
-  <si>
-    <t>APLN</t>
-  </si>
-  <si>
-    <t>ID_1789910582448254</t>
-  </si>
-  <si>
-    <t>ID_1789909327267597</t>
-  </si>
-  <si>
-    <t>trinata</t>
-  </si>
-  <si>
-    <t>trianta</t>
-  </si>
-  <si>
-    <t>triana123</t>
-  </si>
-  <si>
-    <t>Pemasangan</t>
-  </si>
-  <si>
-    <t>trinata@pln.co.id</t>
-  </si>
-  <si>
-    <t>20 kms</t>
-  </si>
-  <si>
-    <t>JTR</t>
-  </si>
-  <si>
-    <t>Perencanaan</t>
-  </si>
-  <si>
     <t>banjar</t>
   </si>
   <si>
-    <t>Arm Tie</t>
-  </si>
-  <si>
-    <t>Aktif</t>
-  </si>
-  <si>
-    <t>ID_1789909449733529</t>
-  </si>
-  <si>
-    <t>supardiana</t>
-  </si>
-  <si>
-    <t>agus150385</t>
-  </si>
-  <si>
-    <t>goespar@gmail.com</t>
-  </si>
-  <si>
-    <t>Administrator</t>
+    <t>tanggal</t>
+  </si>
+  <si>
+    <t>nilai</t>
+  </si>
+  <si>
+    <t>ID_1789926163278337</t>
   </si>
   <si>
     <t>nomor_kontrak</t>
@@ -239,51 +266,42 @@
     <t>nama_penyedia</t>
   </si>
   <si>
-    <t>tanggal</t>
-  </si>
-  <si>
     <t>nilai_kontrak</t>
   </si>
   <si>
     <t>tanggal_kontrak</t>
   </si>
   <si>
-    <t>nilai</t>
-  </si>
-  <si>
     <t>tanggal_mulai</t>
   </si>
   <si>
     <t>tanggal_selesai</t>
   </si>
   <si>
-    <t>ID_1789910714001497</t>
-  </si>
-  <si>
-    <t>149/62.62/ABU/2026</t>
+    <t>ID_1789926177595517</t>
+  </si>
+  <si>
+    <t>ID_1789926703623935</t>
+  </si>
+  <si>
+    <t>152/61.61/ABU/2026</t>
   </si>
   <si>
     <t>PT RADJOE BINTANG</t>
   </si>
   <si>
-    <t>ID_1789910930132850</t>
-  </si>
-  <si>
-    <t>sudah 50</t>
-  </si>
-  <si>
-    <t>ID_178991076493289</t>
-  </si>
-  <si>
-    <t>150/62.62/ABU/2026</t>
+    <t>ID_1789926193090670</t>
+  </si>
+  <si>
+    <t>ID_1789926776817300</t>
+  </si>
+  <si>
+    <t>155/61.61/ABU/2026</t>
   </si>
   <si>
     <t>ARUNA</t>
   </si>
   <si>
-    <t>ID_178991109473268</t>
-  </si>
-  <si>
     <t>material</t>
   </si>
   <si>
@@ -293,6 +311,24 @@
     <t>total</t>
   </si>
   <si>
+    <t>ID_1789898324940512</t>
+  </si>
+  <si>
+    <t>JTM / Distribusi</t>
+  </si>
+  <si>
+    <t>ID_1789910016885530</t>
+  </si>
+  <si>
+    <t>SKUTR / Sambungan Rumah</t>
+  </si>
+  <si>
+    <t>ID_1789918419722905</t>
+  </si>
+  <si>
+    <t>JTM (Jaringan Tegangan Menengah)</t>
+  </si>
+  <si>
     <t>alamat</t>
   </si>
   <si>
@@ -308,33 +344,21 @@
     <t>Jln Gajahmada Singaraja</t>
   </si>
   <si>
-    <t>ID_1789898324940512</t>
-  </si>
-  <si>
     <t>5107051503970001</t>
   </si>
   <si>
     <t>Instalasi</t>
   </si>
   <si>
-    <t>JTM / Distribusi</t>
-  </si>
-  <si>
     <t>ID_1789909618314364</t>
   </si>
   <si>
-    <t>ID_1789910016885530</t>
-  </si>
-  <si>
     <t>tejakula</t>
   </si>
   <si>
     <t>Kontruksi</t>
   </si>
   <si>
-    <t>SKUTR / Sambungan Rumah</t>
-  </si>
-  <si>
     <t>aksi</t>
   </si>
   <si>
@@ -453,6 +477,15 @@
   </si>
   <si>
     <t>83de0457-4619-431c-8efc-fcd23a16b362</t>
+  </si>
+  <si>
+    <t>ID_1789926705448246</t>
+  </si>
+  <si>
+    <t>ID_1789926778753667</t>
+  </si>
+  <si>
+    <t>ID_1789926798072752</t>
   </si>
 </sst>
 </file>
@@ -463,7 +496,7 @@
     <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -491,6 +524,11 @@
     <font>
       <sz val="9.0"/>
       <color theme="1"/>
+      <name val="Menlo"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -508,7 +546,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -521,13 +559,16 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -795,80 +836,54 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H2" s="4">
-        <v>46285.87647300926</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H3" s="4">
-        <v>46285.87789042824</v>
+      <c r="H2" s="5">
+        <v>46286.054823611106</v>
       </c>
     </row>
   </sheetData>
@@ -888,7 +903,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -908,19 +923,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -928,255 +943,288 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46286.07760935185</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46286.07845778935</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46286.078681388884</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1207,27 +1255,27 @@
         <v>5</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2">
         <v>2.0</v>
@@ -1236,21 +1284,21 @@
         <v>2026.0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F2" s="2">
         <v>1.0E8</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="5">
         <v>46285.878641550924</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2">
         <v>1.0</v>
@@ -1259,13 +1307,36 @@
         <v>2026.0</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2">
         <v>2.0E7</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="5">
         <v>46285.88897541667</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="2">
+        <v>5.0E7</v>
+      </c>
+      <c r="H4" s="5">
+        <v>46285.98263940972</v>
       </c>
     </row>
   </sheetData>
@@ -1295,89 +1366,166 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>34</v>
+      <c r="N1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D2" s="2">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K2" s="4">
-        <v>46285.879326423616</v>
+        <v>63</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K2" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="5">
+        <v>46286.050068125</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D3" s="2">
         <v>2.0</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K3" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K3" s="4">
-        <v>46285.88970189815</v>
+      <c r="O3" s="5">
+        <v>46286.0508553125</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K4" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" s="5">
+        <v>46286.062924756945</v>
       </c>
     </row>
   </sheetData>
@@ -1410,131 +1558,225 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I2" s="5">
+        <v>51</v>
+      </c>
+      <c r="I2" s="7">
         <v>1.0</v>
       </c>
-      <c r="J2" s="5">
-        <v>20000.0</v>
-      </c>
-      <c r="K2" s="5">
-        <v>20000.0</v>
-      </c>
-      <c r="L2" s="5">
-        <v>20000.0</v>
-      </c>
-      <c r="M2" s="5">
-        <v>20000.0</v>
-      </c>
-      <c r="N2" s="5">
-        <v>40000.0</v>
-      </c>
-      <c r="O2" s="4">
-        <v>46285.890357233795</v>
+      <c r="J2" s="7">
+        <v>1000000.0</v>
+      </c>
+      <c r="K2" s="7">
+        <v>200000.0</v>
+      </c>
+      <c r="L2" s="7">
+        <v>1000000.0</v>
+      </c>
+      <c r="M2" s="7">
+        <v>200000.0</v>
+      </c>
+      <c r="N2" s="7">
+        <v>1200000.0</v>
+      </c>
+      <c r="O2" s="5">
+        <v>46286.05965200231</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>62</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" s="5">
+        <v>64</v>
+      </c>
+      <c r="I3" s="7">
         <v>1.0</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="7">
         <v>2000.0</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="7">
         <v>2000.0</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3" s="7">
         <v>2000.0</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="7">
         <v>2000.0</v>
       </c>
-      <c r="N3" s="5">
+      <c r="N3" s="7">
         <v>4000.0</v>
       </c>
-      <c r="O3" s="4">
-        <v>46285.89100055555</v>
+      <c r="O3" s="5">
+        <v>46286.06051850694</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I4" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="J4" s="7">
+        <v>20000.0</v>
+      </c>
+      <c r="K4" s="7">
+        <v>20000.0</v>
+      </c>
+      <c r="L4" s="7">
+        <v>20000.0</v>
+      </c>
+      <c r="M4" s="7">
+        <v>20000.0</v>
+      </c>
+      <c r="N4" s="7">
+        <v>40000.0</v>
+      </c>
+      <c r="O4" s="5">
+        <v>46286.061886261574</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="J5" s="7">
+        <v>2000.0</v>
+      </c>
+      <c r="K5" s="7">
+        <v>2000.0</v>
+      </c>
+      <c r="L5" s="7">
+        <v>2000.0</v>
+      </c>
+      <c r="M5" s="7">
+        <v>2000.0</v>
+      </c>
+      <c r="N5" s="7">
+        <v>4000.0</v>
+      </c>
+      <c r="O5" s="5">
+        <v>46286.06381736111</v>
       </c>
     </row>
   </sheetData>
@@ -1567,86 +1809,118 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="7">
-        <v>46280.0</v>
+        <v>59</v>
+      </c>
+      <c r="F2" s="8">
+        <v>46285.0</v>
       </c>
       <c r="G2" s="2">
-        <v>1.0E7</v>
+        <v>2000.0</v>
       </c>
       <c r="H2" s="2">
-        <v>50.0</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J2" s="4">
-        <v>46285.89502467593</v>
+        <v>3.0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J2" s="5">
+        <v>46286.07133423611</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="7">
-        <v>46283.0</v>
+      <c r="F3" s="8">
+        <v>46285.0</v>
       </c>
       <c r="G3" s="2">
-        <v>5.0E7</v>
+        <v>122.0</v>
       </c>
       <c r="H3" s="2">
-        <v>50.0</v>
+        <v>22.0</v>
       </c>
       <c r="I3" s="2">
-        <v>50.0</v>
-      </c>
-      <c r="J3" s="4">
-        <v>46285.89692976852</v>
+        <v>1.0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>46286.07149994213</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="8">
+        <v>46285.0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>22222.0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>23.0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>22.0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>46286.07167928241</v>
       </c>
     </row>
   </sheetData>
@@ -1673,89 +1947,95 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G2" s="2">
-        <v>1.9E7</v>
-      </c>
-      <c r="H2" s="7">
-        <v>46266.0</v>
-      </c>
-      <c r="I2" s="7">
-        <v>46275.0</v>
-      </c>
-      <c r="J2" s="7">
-        <v>46284.0</v>
+        <v>1223.0</v>
+      </c>
+      <c r="H2" s="8">
+        <v>46267.0</v>
+      </c>
+      <c r="I2" s="8">
+        <v>46274.0</v>
+      </c>
+      <c r="J2" s="8">
+        <v>46291.0</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G3" s="2">
-        <v>9.0E7</v>
-      </c>
-      <c r="H3" s="7">
-        <v>46267.0</v>
-      </c>
-      <c r="I3" s="7">
-        <v>46270.0</v>
-      </c>
-      <c r="J3" s="7">
-        <v>46281.0</v>
+        <v>533.0</v>
+      </c>
+      <c r="H3" s="8">
+        <v>46268.0</v>
+      </c>
+      <c r="I3" s="8">
+        <v>46276.0</v>
+      </c>
+      <c r="J3" s="8">
+        <v>46284.0</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1771,6 +2051,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="3" max="3" width="20.38"/>
+    <col customWidth="1" min="11" max="11" width="19.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1781,28 +2062,28 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>15</v>
@@ -1810,54 +2091,80 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="5">
+        <v>64</v>
+      </c>
+      <c r="G2" s="7">
         <v>1.0</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="7">
         <v>20000.0</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="7">
         <v>20000.0</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="7">
         <v>20000.0</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>62</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="5">
+        <v>64</v>
+      </c>
+      <c r="G3" s="7">
         <v>1.0</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="7">
         <v>2000.0</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="7">
         <v>2000.0</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="7">
         <v>2000.0</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="H4" s="7">
+        <v>1000000.0</v>
+      </c>
+      <c r="I4" s="7">
+        <v>200000.0</v>
+      </c>
+      <c r="J4" s="7">
+        <v>1000000.0</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1880,56 +2187,56 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D2" s="2">
         <v>8.1999348678E10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D3" s="2">
         <v>1112334.0</v>
@@ -1938,10 +2245,10 @@
         <v>1111111.0</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1961,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
